--- a/resources/Programmes/Programmeclasse4ecollege.xlsx
+++ b/resources/Programmes/Programmeclasse4ecollege.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\JANGAA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JEANNE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33AAB5B8-FBC9-4B82-8DB6-D67F9976B0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7155"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="216">
   <si>
     <t>Matière</t>
   </si>
@@ -732,12 +731,15 @@
   </si>
   <si>
     <t>Questions de compréhension orale et écrite</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1024,12 +1026,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA53"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="8" max="9" width="14.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1078,7 +1090,7 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1107,7 +1119,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>215</v>
+      </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1133,7 +1148,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>215</v>
+      </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1159,73 +1177,108 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="5" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>215</v>
+      </c>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>215</v>
+      </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>215</v>
+      </c>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>15</v>
@@ -1234,203 +1287,317 @@
         <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B9" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>59</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>215</v>
+      </c>
       <c r="B12" s="5" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="H12" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>68</v>
+        <v>77</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>73</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="H15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>215</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>215</v>
+      </c>
       <c r="B18" s="4" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>215</v>
+      </c>
       <c r="B19" s="4" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>15</v>
@@ -1439,24 +1606,27 @@
         <v>83</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>215</v>
+      </c>
       <c r="B20" s="4" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>99</v>
@@ -1465,188 +1635,288 @@
         <v>99</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="B21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>102</v>
+        <v>215</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B22" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>107</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" t="s">
+        <v>215</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>99</v>
+        <v>127</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>112</v>
+        <v>128</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>83</v>
+        <v>131</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
+        <v>215</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>137</v>
+      </c>
+      <c r="I24" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" t="s">
+        <v>215</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="72" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I26" s="4" t="s">
+      <c r="H28" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="C28" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I28" s="6"/>
-    </row>
-    <row r="30" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>215</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="129" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>134</v>
+        <v>159</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>59</v>
@@ -1655,368 +1925,330 @@
         <v>59</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
-      <c r="C31" s="5" t="s">
-        <v>138</v>
+        <v>164</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+        <v>168</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="H31" s="4" t="s">
-        <v>141</v>
+        <v>169</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
-      <c r="C32" s="5" t="s">
-        <v>142</v>
+      <c r="A32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+        <v>174</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="H32" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="72" x14ac:dyDescent="0.25">
-      <c r="C33" s="5" t="s">
-        <v>146</v>
+        <v>175</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+        <v>179</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="H33" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="6"/>
+        <v>180</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="D35" s="4" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F35" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I35" s="4" t="s">
+      <c r="H37" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="38" spans="1:9" ht="129" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>161</v>
+    <row r="38" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F38" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="I38" s="4" t="s">
+      <c r="H40" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="41" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>170</v>
+    <row r="41" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>215</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>59</v>
+        <v>213</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="44" spans="1:9" ht="86.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
-      <c r="C45" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" spans="1:9" ht="72" x14ac:dyDescent="0.25">
-      <c r="C46" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I46" s="6"/>
-    </row>
-    <row r="48" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
-      <c r="C49" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="I49" s="6"/>
-    </row>
-    <row r="50" spans="1:9" ht="86.25" x14ac:dyDescent="0.25">
-      <c r="C50" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I50" s="6"/>
-    </row>
-    <row r="52" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="I53" s="6"/>
+      <c r="I41" s="6" t="s">
+        <v>215</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/Programmes/Programmeclasse4ecollege.xlsx
+++ b/resources/Programmes/Programmeclasse4ecollege.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JEANNE\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\gestionscolaire\resources\Programmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="218">
   <si>
     <t>Matière</t>
   </si>
@@ -734,13 +734,19 @@
   </si>
   <si>
     <t>null</t>
+  </si>
+  <si>
+    <t>heure_debut</t>
+  </si>
+  <si>
+    <t>heure_fin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -775,6 +781,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -796,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -811,6 +823,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1030,7 +1045,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA41"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -1040,10 +1055,13 @@
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="9" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,10 +1087,14 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -1089,8 +1111,10 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
-    </row>
-    <row r="2" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+    </row>
+    <row r="2" spans="1:29" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1115,11 +1139,17 @@
       <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>215</v>
       </c>
@@ -1144,11 +1174,17 @@
       <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>215</v>
       </c>
@@ -1173,11 +1209,17 @@
       <c r="H4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -1202,11 +1244,17 @@
       <c r="H5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>215</v>
       </c>
@@ -1231,11 +1279,17 @@
       <c r="H6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>215</v>
       </c>
@@ -1260,11 +1314,17 @@
       <c r="H7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>215</v>
       </c>
@@ -1290,10 +1350,16 @@
         <v>51</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -1319,10 +1385,16 @@
         <v>60</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>215</v>
       </c>
@@ -1347,11 +1419,17 @@
       <c r="H10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1377,10 +1455,16 @@
         <v>72</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>215</v>
       </c>
@@ -1405,11 +1489,17 @@
       <c r="H12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="I12" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>78</v>
       </c>
@@ -1435,10 +1525,16 @@
         <v>84</v>
       </c>
       <c r="I13" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>215</v>
       </c>
@@ -1464,10 +1560,16 @@
         <v>89</v>
       </c>
       <c r="I14" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>215</v>
       </c>
@@ -1493,10 +1595,16 @@
         <v>94</v>
       </c>
       <c r="I15" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K15" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>215</v>
       </c>
@@ -1522,10 +1630,16 @@
         <v>100</v>
       </c>
       <c r="I16" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>215</v>
       </c>
@@ -1551,10 +1665,16 @@
         <v>105</v>
       </c>
       <c r="I17" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>215</v>
       </c>
@@ -1580,10 +1700,16 @@
         <v>110</v>
       </c>
       <c r="I18" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>215</v>
       </c>
@@ -1609,10 +1735,16 @@
         <v>114</v>
       </c>
       <c r="I19" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>215</v>
       </c>
@@ -1638,10 +1770,16 @@
         <v>119</v>
       </c>
       <c r="I20" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>120</v>
       </c>
@@ -1667,10 +1805,16 @@
         <v>124</v>
       </c>
       <c r="I21" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>215</v>
       </c>
@@ -1695,11 +1839,17 @@
       <c r="H22" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="I22" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>215</v>
       </c>
@@ -1724,11 +1874,17 @@
       <c r="H23" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="I23" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>133</v>
       </c>
@@ -1753,11 +1909,17 @@
       <c r="H24" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="I24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="I24" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K24" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>215</v>
       </c>
@@ -1782,11 +1944,17 @@
       <c r="H25" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="I25" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K25" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>215</v>
       </c>
@@ -1811,11 +1979,17 @@
       <c r="H26" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="I26" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="72" x14ac:dyDescent="0.25">
+      <c r="I26" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>215</v>
       </c>
@@ -1840,11 +2014,17 @@
       <c r="H27" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="I27" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="I27" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K27" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="72" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>150</v>
       </c>
@@ -1870,10 +2050,16 @@
         <v>154</v>
       </c>
       <c r="I28" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>215</v>
       </c>
@@ -1898,11 +2084,17 @@
       <c r="H29" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="129" x14ac:dyDescent="0.25">
+      <c r="I29" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="72" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>159</v>
       </c>
@@ -1928,10 +2120,16 @@
         <v>164</v>
       </c>
       <c r="I30" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>215</v>
       </c>
@@ -1956,11 +2154,17 @@
       <c r="H31" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+      <c r="I31" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="72" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>170</v>
       </c>
@@ -1986,10 +2190,16 @@
         <v>175</v>
       </c>
       <c r="I32" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>215</v>
       </c>
@@ -2014,11 +2224,17 @@
       <c r="H33" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="I33" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="I33" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="72" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>181</v>
       </c>
@@ -2044,10 +2260,16 @@
         <v>185</v>
       </c>
       <c r="I34" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K34" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>215</v>
       </c>
@@ -2072,11 +2294,17 @@
       <c r="H35" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="I35" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="72" x14ac:dyDescent="0.25">
+      <c r="I35" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>215</v>
       </c>
@@ -2101,11 +2329,17 @@
       <c r="H36" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="I36" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="I36" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="72" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>194</v>
       </c>
@@ -2131,10 +2365,16 @@
         <v>198</v>
       </c>
       <c r="I37" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="100.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>215</v>
       </c>
@@ -2159,11 +2399,17 @@
       <c r="H38" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="I38" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="I38" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>215</v>
       </c>
@@ -2188,11 +2434,17 @@
       <c r="H39" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="I39" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="I39" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="72" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>207</v>
       </c>
@@ -2218,10 +2470,16 @@
         <v>210</v>
       </c>
       <c r="I40" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K40" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>215</v>
       </c>
@@ -2246,7 +2504,13 @@
       <c r="H41" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="K41" s="6" t="s">
         <v>215</v>
       </c>
     </row>
